--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3458,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113291488</v>
+        <v>113291497</v>
       </c>
       <c r="B25" t="n">
-        <v>104364</v>
+        <v>89504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,27 +3474,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3565,10 +3572,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113291497</v>
+        <v>113291488</v>
       </c>
       <c r="B26" t="n">
-        <v>89488</v>
+        <v>104380</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3581,34 +3588,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>113291497</v>
       </c>
       <c r="B25" t="n">
-        <v>89504</v>
+        <v>89516</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>113291488</v>
       </c>
       <c r="B26" t="n">
-        <v>104380</v>
+        <v>104394</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3458,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113291497</v>
+        <v>113291488</v>
       </c>
       <c r="B25" t="n">
-        <v>89516</v>
+        <v>104394</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,34 +3474,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3572,10 +3565,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113291488</v>
+        <v>113291497</v>
       </c>
       <c r="B26" t="n">
-        <v>104394</v>
+        <v>89516</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3588,27 +3581,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>113291488</v>
       </c>
       <c r="B25" t="n">
-        <v>104394</v>
+        <v>104416</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>113291497</v>
       </c>
       <c r="B26" t="n">
-        <v>89516</v>
+        <v>89538</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3458,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113291488</v>
+        <v>113291497</v>
       </c>
       <c r="B25" t="n">
-        <v>104416</v>
+        <v>89542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,27 +3474,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3565,10 +3572,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113291497</v>
+        <v>113291488</v>
       </c>
       <c r="B26" t="n">
-        <v>89538</v>
+        <v>104420</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3581,34 +3588,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3458,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113291497</v>
+        <v>113291488</v>
       </c>
       <c r="B25" t="n">
-        <v>89542</v>
+        <v>104420</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,34 +3474,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3572,10 +3565,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113291488</v>
+        <v>113291497</v>
       </c>
       <c r="B26" t="n">
-        <v>104420</v>
+        <v>89542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3588,27 +3581,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>113291488</v>
       </c>
       <c r="B25" t="n">
-        <v>104420</v>
+        <v>104426</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>113291497</v>
       </c>
       <c r="B26" t="n">
-        <v>89542</v>
+        <v>89548</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3458,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113291488</v>
+        <v>113291497</v>
       </c>
       <c r="B25" t="n">
-        <v>104426</v>
+        <v>89548</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,27 +3474,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3565,10 +3572,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113291497</v>
+        <v>113291488</v>
       </c>
       <c r="B26" t="n">
-        <v>89548</v>
+        <v>104426</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3581,34 +3588,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>113291497</v>
       </c>
       <c r="B25" t="n">
-        <v>89548</v>
+        <v>89555</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>113291488</v>
       </c>
       <c r="B26" t="n">
-        <v>104426</v>
+        <v>104433</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -4256,11 +4256,11 @@
         <v>115877895</v>
       </c>
       <c r="B32" t="n">
-        <v>83054</v>
+        <v>83201</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4394,11 +4394,11 @@
         <v>115877640</v>
       </c>
       <c r="B33" t="n">
-        <v>83054</v>
+        <v>83201</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -4256,7 +4256,7 @@
         <v>115877895</v>
       </c>
       <c r="B32" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>115877640</v>
       </c>
       <c r="B33" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5566,6 +5566,330 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122878312</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91564</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skinnerud, Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>446352</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6585665</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122881299</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vallshagen, Vallshagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>446136</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6585567</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122881169</v>
+      </c>
+      <c r="B45" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vallshagen, Vallshagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>446130</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6585613</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122878312</v>
+        <v>122881169</v>
       </c>
       <c r="B43" t="n">
-        <v>91564</v>
+        <v>83376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,38 +5580,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446352</v>
+        <v>446130</v>
       </c>
       <c r="R43" t="n">
-        <v>6585665</v>
+        <v>6585613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5670,10 +5679,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122881299</v>
+        <v>122878312</v>
       </c>
       <c r="B44" t="n">
-        <v>83376</v>
+        <v>91564</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,47 +5691,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446136</v>
+        <v>446352</v>
       </c>
       <c r="R44" t="n">
-        <v>6585567</v>
+        <v>6585665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122881169</v>
+        <v>122881299</v>
       </c>
       <c r="B45" t="n">
         <v>83376</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446130</v>
+        <v>446136</v>
       </c>
       <c r="R45" t="n">
-        <v>6585613</v>
+        <v>6585567</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5889,6 +5889,120 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122901055</v>
+      </c>
+      <c r="B46" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>446135</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6585481</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122881169</v>
+        <v>122878312</v>
       </c>
       <c r="B43" t="n">
-        <v>83376</v>
+        <v>91564</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,47 +5580,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446130</v>
+        <v>446352</v>
       </c>
       <c r="R43" t="n">
-        <v>6585613</v>
+        <v>6585665</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5679,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122878312</v>
+        <v>122881169</v>
       </c>
       <c r="B44" t="n">
-        <v>91564</v>
+        <v>83376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,38 +5682,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446352</v>
+        <v>446130</v>
       </c>
       <c r="R44" t="n">
-        <v>6585665</v>
+        <v>6585613</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122878312</v>
+        <v>122881169</v>
       </c>
       <c r="B43" t="n">
-        <v>91564</v>
+        <v>83376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,38 +5580,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446352</v>
+        <v>446130</v>
       </c>
       <c r="R43" t="n">
-        <v>6585665</v>
+        <v>6585613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5670,7 +5679,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122881169</v>
+        <v>122881299</v>
       </c>
       <c r="B44" t="n">
         <v>83376</v>
@@ -5705,7 +5714,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5719,10 +5728,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446130</v>
+        <v>446136</v>
       </c>
       <c r="R44" t="n">
-        <v>6585613</v>
+        <v>6585567</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5781,10 +5790,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122881299</v>
+        <v>122878312</v>
       </c>
       <c r="B45" t="n">
-        <v>83376</v>
+        <v>91564</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5793,47 +5802,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446136</v>
+        <v>446352</v>
       </c>
       <c r="R45" t="n">
-        <v>6585567</v>
+        <v>6585665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5568,7 +5568,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122881169</v>
+        <v>122881299</v>
       </c>
       <c r="B43" t="n">
         <v>83376</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446130</v>
+        <v>446136</v>
       </c>
       <c r="R43" t="n">
-        <v>6585613</v>
+        <v>6585567</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122881299</v>
+        <v>122881169</v>
       </c>
       <c r="B44" t="n">
         <v>83376</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446136</v>
+        <v>446130</v>
       </c>
       <c r="R44" t="n">
-        <v>6585567</v>
+        <v>6585613</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5793,7 +5793,7 @@
         <v>122878312</v>
       </c>
       <c r="B45" t="n">
-        <v>91564</v>
+        <v>91572</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122881299</v>
+        <v>122878312</v>
       </c>
       <c r="B43" t="n">
-        <v>83376</v>
+        <v>91572</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,47 +5580,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446136</v>
+        <v>446352</v>
       </c>
       <c r="R43" t="n">
-        <v>6585567</v>
+        <v>6585665</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5790,10 +5781,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122878312</v>
+        <v>122881299</v>
       </c>
       <c r="B45" t="n">
-        <v>91572</v>
+        <v>83376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5802,38 +5793,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446352</v>
+        <v>446136</v>
       </c>
       <c r="R45" t="n">
-        <v>6585665</v>
+        <v>6585567</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5670,7 +5670,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122881169</v>
+        <v>122881299</v>
       </c>
       <c r="B44" t="n">
         <v>83376</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446130</v>
+        <v>446136</v>
       </c>
       <c r="R44" t="n">
-        <v>6585613</v>
+        <v>6585567</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122881299</v>
+        <v>122881169</v>
       </c>
       <c r="B45" t="n">
         <v>83376</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446136</v>
+        <v>446130</v>
       </c>
       <c r="R45" t="n">
-        <v>6585567</v>
+        <v>6585613</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122878312</v>
+        <v>122881169</v>
       </c>
       <c r="B43" t="n">
-        <v>91572</v>
+        <v>83376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,38 +5580,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446352</v>
+        <v>446130</v>
       </c>
       <c r="R43" t="n">
-        <v>6585665</v>
+        <v>6585613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5781,10 +5790,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122881169</v>
+        <v>122878312</v>
       </c>
       <c r="B45" t="n">
-        <v>83376</v>
+        <v>91572</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5793,47 +5802,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446130</v>
+        <v>446352</v>
       </c>
       <c r="R45" t="n">
-        <v>6585613</v>
+        <v>6585665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6004,6 +6004,374 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123379164</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>N Skinneruds skjutbana, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>446115</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6585496</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tove Thomasson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tove Thomasson, Bengt Hansson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123379163</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>N Skinneruds skjutbana, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>446115</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6585496</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tove Thomasson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tove Thomasson, Bengt Hansson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123379162</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>N Skinneruds skjutbana, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>446115</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6585496</v>
+      </c>
+      <c r="S49" t="n">
+        <v>9</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tove Thomasson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tove Thomasson, Bengt Hansson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5571,7 +5571,7 @@
         <v>122881169</v>
       </c>
       <c r="B43" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122881299</v>
+        <v>122878312</v>
       </c>
       <c r="B44" t="n">
-        <v>83376</v>
+        <v>91575</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,47 +5691,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446136</v>
+        <v>446352</v>
       </c>
       <c r="R44" t="n">
-        <v>6585567</v>
+        <v>6585665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5790,10 +5781,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122878312</v>
+        <v>122881299</v>
       </c>
       <c r="B45" t="n">
-        <v>91572</v>
+        <v>83379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5802,38 +5793,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446352</v>
+        <v>446136</v>
       </c>
       <c r="R45" t="n">
-        <v>6585665</v>
+        <v>6585567</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5895,7 +5895,7 @@
         <v>122901055</v>
       </c>
       <c r="B46" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123379164</v>
+        <v>123379163</v>
       </c>
       <c r="B47" t="n">
-        <v>83376</v>
+        <v>57851</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,30 +6018,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1445</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6095,11 +6104,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6126,10 +6130,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123379163</v>
+        <v>123379162</v>
       </c>
       <c r="B48" t="n">
-        <v>57848</v>
+        <v>57634</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6138,30 +6142,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6250,10 +6254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379162</v>
+        <v>123379164</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>83379</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6262,39 +6266,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>1445</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6348,6 +6343,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5571,7 +5571,7 @@
         <v>122881169</v>
       </c>
       <c r="B43" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>122878312</v>
       </c>
       <c r="B44" t="n">
-        <v>91575</v>
+        <v>91577</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>122881299</v>
       </c>
       <c r="B45" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>122901055</v>
       </c>
       <c r="B46" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123379163</v>
+        <v>123379164</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>83381</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,39 +6018,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>1445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6104,6 +6095,11 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6254,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379164</v>
+        <v>123379163</v>
       </c>
       <c r="B49" t="n">
-        <v>83379</v>
+        <v>57851</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,30 +6262,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1445</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6343,11 +6348,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122881169</v>
+        <v>122881299</v>
       </c>
       <c r="B43" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446130</v>
+        <v>446136</v>
       </c>
       <c r="R43" t="n">
-        <v>6585613</v>
+        <v>6585567</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5682,7 +5682,7 @@
         <v>122878312</v>
       </c>
       <c r="B44" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122881299</v>
+        <v>122881169</v>
       </c>
       <c r="B45" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446136</v>
+        <v>446130</v>
       </c>
       <c r="R45" t="n">
-        <v>6585567</v>
+        <v>6585613</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5895,7 +5895,7 @@
         <v>122901055</v>
       </c>
       <c r="B46" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123379164</v>
+        <v>123379163</v>
       </c>
       <c r="B47" t="n">
-        <v>83381</v>
+        <v>57851</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,30 +6018,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1445</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6095,11 +6104,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6250,10 +6254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379163</v>
+        <v>123379164</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>83383</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6262,39 +6266,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>1445</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6350,6 +6345,11 @@
           <t>13:58</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6371,6 +6371,235 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123516486</v>
+      </c>
+      <c r="B50" t="n">
+        <v>83383</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>446263</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6585641</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123519052</v>
+      </c>
+      <c r="B51" t="n">
+        <v>83386</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>N om Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>446284</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6585649</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -5568,10 +5568,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122881299</v>
+        <v>122878312</v>
       </c>
       <c r="B43" t="n">
-        <v>83383</v>
+        <v>91586</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,47 +5580,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vallshagen, Vallshagen, Vrm</t>
+          <t>Skinnerud, Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446136</v>
+        <v>446352</v>
       </c>
       <c r="R43" t="n">
-        <v>6585567</v>
+        <v>6585665</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5679,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122878312</v>
+        <v>122881299</v>
       </c>
       <c r="B44" t="n">
-        <v>91583</v>
+        <v>83386</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,38 +5682,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skinnerud, Skinnerud, Vrm</t>
+          <t>Vallshagen, Vallshagen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446352</v>
+        <v>446136</v>
       </c>
       <c r="R44" t="n">
-        <v>6585665</v>
+        <v>6585567</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5784,7 +5784,7 @@
         <v>122881169</v>
       </c>
       <c r="B45" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>122901055</v>
       </c>
       <c r="B46" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123379163</v>
+        <v>123379164</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>83386</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,39 +6018,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>1445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6104,6 +6095,11 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6254,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379164</v>
+        <v>123379163</v>
       </c>
       <c r="B49" t="n">
-        <v>83383</v>
+        <v>57851</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,30 +6262,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1445</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6343,11 +6348,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6374,10 +6374,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123516486</v>
+        <v>123519052</v>
       </c>
       <c r="B50" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6417,18 +6417,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skinnerud, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446263</v>
+        <v>446284</v>
       </c>
       <c r="R50" t="n">
-        <v>6585641</v>
+        <v>6585649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6469,30 +6467,25 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123519052</v>
+        <v>123516486</v>
       </c>
       <c r="B51" t="n">
         <v>83386</v>
@@ -6535,16 +6528,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446284</v>
+        <v>446263</v>
       </c>
       <c r="R51" t="n">
-        <v>6585649</v>
+        <v>6585641</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6585,21 +6580,26 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6006,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123379164</v>
+        <v>123379163</v>
       </c>
       <c r="B47" t="n">
-        <v>83386</v>
+        <v>57857</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,30 +6018,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1445</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6095,11 +6104,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6129,7 +6133,7 @@
         <v>123379162</v>
       </c>
       <c r="B48" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6250,10 +6254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379163</v>
+        <v>123379164</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>83395</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6262,39 +6266,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>1445</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6348,6 +6343,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6374,10 +6374,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123519052</v>
+        <v>123516486</v>
       </c>
       <c r="B50" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6417,16 +6417,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446284</v>
+        <v>446263</v>
       </c>
       <c r="R50" t="n">
-        <v>6585649</v>
+        <v>6585641</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6467,28 +6469,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123516486</v>
+        <v>123519052</v>
       </c>
       <c r="B51" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6528,18 +6535,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skinnerud, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446263</v>
+        <v>446284</v>
       </c>
       <c r="R51" t="n">
-        <v>6585641</v>
+        <v>6585649</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6580,26 +6585,21 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6006,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123379163</v>
+        <v>123379164</v>
       </c>
       <c r="B47" t="n">
-        <v>57857</v>
+        <v>83400</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,39 +6018,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>1445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6104,6 +6095,11 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6130,10 +6126,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123379162</v>
+        <v>123379163</v>
       </c>
       <c r="B48" t="n">
-        <v>57640</v>
+        <v>57860</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6142,30 +6138,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6254,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379164</v>
+        <v>123379162</v>
       </c>
       <c r="B49" t="n">
-        <v>83395</v>
+        <v>57643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,30 +6262,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1445</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6343,11 +6348,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6374,10 +6374,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123516486</v>
+        <v>123519052</v>
       </c>
       <c r="B50" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6417,18 +6417,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skinnerud, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446263</v>
+        <v>446284</v>
       </c>
       <c r="R50" t="n">
-        <v>6585641</v>
+        <v>6585649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6469,33 +6467,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123519052</v>
+        <v>123516486</v>
       </c>
       <c r="B51" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6535,16 +6528,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446284</v>
+        <v>446263</v>
       </c>
       <c r="R51" t="n">
-        <v>6585649</v>
+        <v>6585641</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6585,21 +6580,26 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6009,7 +6009,7 @@
         <v>123379164</v>
       </c>
       <c r="B47" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6126,10 +6126,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123379163</v>
+        <v>123379162</v>
       </c>
       <c r="B48" t="n">
-        <v>57860</v>
+        <v>57644</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6138,30 +6138,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123379162</v>
+        <v>123379163</v>
       </c>
       <c r="B49" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6262,30 +6262,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -6377,7 +6377,7 @@
         <v>123519052</v>
       </c>
       <c r="B50" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>123516486</v>
       </c>
       <c r="B51" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6600,6 +6600,365 @@
           <t>Uppföljning bombmurkla 2025</t>
         </is>
       </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123936321</v>
+      </c>
+      <c r="B52" t="n">
+        <v>100682</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vallshagen, Vallshagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>446039</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6585698</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marianne Pasanen-Mortensen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marianne Pasanen-Mortensen, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123935938</v>
+      </c>
+      <c r="B53" t="n">
+        <v>83402</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skinneruds skjutbana N om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>446190</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6585639</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123936010</v>
+      </c>
+      <c r="B54" t="n">
+        <v>83402</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skinneruds skjutbana N om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>446253</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6585661</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Marianne Pasanen-Mortensen, Uno Skog</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123935938</v>
+        <v>123936133</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446190</v>
+        <v>446264</v>
       </c>
       <c r="R54" t="n">
-        <v>6585639</v>
+        <v>6585646</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123936133</v>
+        <v>123935663</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7013,19 +7013,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446264</v>
+        <v>446115</v>
       </c>
       <c r="R55" t="n">
-        <v>6585646</v>
+        <v>6585635</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7054,7 +7056,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7064,7 +7066,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,6 +7080,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7095,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935663</v>
+        <v>123935938</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7130,7 +7138,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7138,18 +7146,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446115</v>
+        <v>446190</v>
       </c>
       <c r="R56" t="n">
-        <v>6585635</v>
+        <v>6585639</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7205,7 +7206,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123936010</v>
+        <v>123935938</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446253</v>
+        <v>446190</v>
       </c>
       <c r="R53" t="n">
-        <v>6585661</v>
+        <v>6585639</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7103,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935938</v>
+        <v>123936010</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446190</v>
+        <v>446253</v>
       </c>
       <c r="R56" t="n">
-        <v>6585639</v>
+        <v>6585661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123936133</v>
+        <v>123936010</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446264</v>
+        <v>446253</v>
       </c>
       <c r="R54" t="n">
-        <v>6585646</v>
+        <v>6585661</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7103,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123936010</v>
+        <v>123936133</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7152,13 +7152,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446253</v>
+        <v>446264</v>
       </c>
       <c r="R56" t="n">
-        <v>6585661</v>
+        <v>6585646</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123936010</v>
+        <v>123935663</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6888,16 +6888,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446253</v>
+        <v>446115</v>
       </c>
       <c r="R54" t="n">
-        <v>6585661</v>
+        <v>6585635</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6929,7 +6931,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6941,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6948,6 +6955,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6970,7 +6978,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935663</v>
+        <v>123936010</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7013,18 +7021,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446115</v>
+        <v>446253</v>
       </c>
       <c r="R55" t="n">
-        <v>6585635</v>
+        <v>6585661</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7056,7 +7062,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7066,12 +7072,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,7 +7081,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123935663</v>
+        <v>123936133</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6888,21 +6888,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446115</v>
+        <v>446264</v>
       </c>
       <c r="R54" t="n">
-        <v>6585635</v>
+        <v>6585646</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6931,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6941,12 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6955,7 +6948,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6978,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123936010</v>
+        <v>123935663</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7021,16 +7013,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446253</v>
+        <v>446115</v>
       </c>
       <c r="R55" t="n">
-        <v>6585661</v>
+        <v>6585635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7062,7 +7056,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7072,7 +7066,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7081,6 +7080,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7103,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123936133</v>
+        <v>123936010</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7152,13 +7152,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446264</v>
+        <v>446253</v>
       </c>
       <c r="R56" t="n">
-        <v>6585646</v>
+        <v>6585661</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123935938</v>
+        <v>123936010</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446190</v>
+        <v>446253</v>
       </c>
       <c r="R53" t="n">
-        <v>6585639</v>
+        <v>6585661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935663</v>
+        <v>123935938</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7013,18 +7013,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446115</v>
+        <v>446190</v>
       </c>
       <c r="R55" t="n">
-        <v>6585635</v>
+        <v>6585639</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7056,7 +7054,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7066,12 +7064,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,7 +7073,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7092,7 +7084,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7103,7 +7095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123936010</v>
+        <v>123935663</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7146,16 +7138,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446253</v>
+        <v>446115</v>
       </c>
       <c r="R56" t="n">
-        <v>6585661</v>
+        <v>6585635</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7206,6 +7205,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123936010</v>
+        <v>123935938</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446253</v>
+        <v>446190</v>
       </c>
       <c r="R53" t="n">
-        <v>6585661</v>
+        <v>6585639</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935938</v>
+        <v>123935663</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7013,16 +7013,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446190</v>
+        <v>446115</v>
       </c>
       <c r="R55" t="n">
-        <v>6585639</v>
+        <v>6585635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7054,7 +7056,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7064,7 +7066,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,6 +7080,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7084,7 +7092,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7095,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935663</v>
+        <v>123936010</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7138,18 +7146,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446115</v>
+        <v>446253</v>
       </c>
       <c r="R56" t="n">
-        <v>6585635</v>
+        <v>6585661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7205,7 +7206,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123936010</v>
+        <v>123936133</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446253</v>
+        <v>446264</v>
       </c>
       <c r="R53" t="n">
-        <v>6585661</v>
+        <v>6585646</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123936133</v>
+        <v>123935938</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446264</v>
+        <v>446190</v>
       </c>
       <c r="R54" t="n">
-        <v>6585646</v>
+        <v>6585639</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935938</v>
+        <v>123935663</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7013,16 +7013,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446190</v>
+        <v>446115</v>
       </c>
       <c r="R55" t="n">
-        <v>6585639</v>
+        <v>6585635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7054,7 +7056,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7064,7 +7066,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,6 +7080,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7084,7 +7092,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7095,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935663</v>
+        <v>123936010</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7138,18 +7146,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446115</v>
+        <v>446253</v>
       </c>
       <c r="R56" t="n">
-        <v>6585635</v>
+        <v>6585661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7205,7 +7206,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123936133</v>
+        <v>123935938</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446264</v>
+        <v>446190</v>
       </c>
       <c r="R53" t="n">
-        <v>6585646</v>
+        <v>6585639</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123935938</v>
+        <v>123936133</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446190</v>
+        <v>446264</v>
       </c>
       <c r="R54" t="n">
-        <v>6585639</v>
+        <v>6585646</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123935938</v>
+        <v>123935663</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6763,16 +6763,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446190</v>
+        <v>446115</v>
       </c>
       <c r="R53" t="n">
-        <v>6585639</v>
+        <v>6585635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6804,7 +6806,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6816,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6823,6 +6830,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6834,7 +6842,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6845,7 +6853,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123936133</v>
+        <v>123936010</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6894,13 +6902,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446264</v>
+        <v>446253</v>
       </c>
       <c r="R54" t="n">
-        <v>6585646</v>
+        <v>6585661</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6937,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6947,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6970,7 +6978,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935663</v>
+        <v>123936133</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7013,21 +7021,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446115</v>
+        <v>446264</v>
       </c>
       <c r="R55" t="n">
-        <v>6585635</v>
+        <v>6585646</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7056,7 +7062,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7066,12 +7072,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,7 +7081,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7103,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123936010</v>
+        <v>123935938</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446253</v>
+        <v>446190</v>
       </c>
       <c r="R56" t="n">
-        <v>6585661</v>
+        <v>6585639</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123935663</v>
+        <v>123936133</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6763,21 +6763,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446115</v>
+        <v>446264</v>
       </c>
       <c r="R53" t="n">
-        <v>6585635</v>
+        <v>6585646</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6806,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6816,12 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6830,7 +6823,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6978,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123936133</v>
+        <v>123935663</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7021,19 +7013,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446264</v>
+        <v>446115</v>
       </c>
       <c r="R55" t="n">
-        <v>6585646</v>
+        <v>6585635</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7062,7 +7056,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7072,7 +7066,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7081,6 +7080,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123936133</v>
+        <v>123935938</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446264</v>
+        <v>446190</v>
       </c>
       <c r="R53" t="n">
-        <v>6585646</v>
+        <v>6585639</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123936010</v>
+        <v>123936133</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446253</v>
+        <v>446264</v>
       </c>
       <c r="R54" t="n">
-        <v>6585661</v>
+        <v>6585646</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7103,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935938</v>
+        <v>123936010</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446190</v>
+        <v>446253</v>
       </c>
       <c r="R56" t="n">
-        <v>6585639</v>
+        <v>6585661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123935938</v>
+        <v>123936010</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446190</v>
+        <v>446253</v>
       </c>
       <c r="R53" t="n">
-        <v>6585639</v>
+        <v>6585661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6845,7 +6845,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123936133</v>
+        <v>123935938</v>
       </c>
       <c r="B54" t="n">
         <v>83424</v>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446264</v>
+        <v>446190</v>
       </c>
       <c r="R54" t="n">
-        <v>6585646</v>
+        <v>6585639</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Marianne Pasanen-Mortensen, Uno Skog</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935663</v>
+        <v>123936133</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7013,21 +7013,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446115</v>
+        <v>446264</v>
       </c>
       <c r="R55" t="n">
-        <v>6585635</v>
+        <v>6585646</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7056,7 +7054,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7066,12 +7064,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,7 +7073,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7103,7 +7095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123936010</v>
+        <v>123935663</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7146,16 +7138,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446253</v>
+        <v>446115</v>
       </c>
       <c r="R56" t="n">
-        <v>6585661</v>
+        <v>6585635</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7187,7 +7181,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7197,7 +7191,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7206,6 +7205,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6720,7 +6720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123936010</v>
+        <v>123936133</v>
       </c>
       <c r="B53" t="n">
         <v>83424</v>
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446253</v>
+        <v>446264</v>
       </c>
       <c r="R53" t="n">
-        <v>6585661</v>
+        <v>6585646</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marianne Pasanen-Mortensen, Uno Skog</t>
+          <t>Uno Skog, Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123936133</v>
+        <v>123936010</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7019,13 +7019,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446264</v>
+        <v>446253</v>
       </c>
       <c r="R55" t="n">
-        <v>6585646</v>
+        <v>6585661</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -6970,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123936010</v>
+        <v>123935663</v>
       </c>
       <c r="B55" t="n">
         <v>83424</v>
@@ -7013,16 +7013,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446253</v>
+        <v>446115</v>
       </c>
       <c r="R55" t="n">
-        <v>6585661</v>
+        <v>6585635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7054,7 +7056,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7064,7 +7066,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,6 +7080,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7095,7 +7103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935663</v>
+        <v>123936010</v>
       </c>
       <c r="B56" t="n">
         <v>83424</v>
@@ -7138,18 +7146,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skinneruds skjutbana N om, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446115</v>
+        <v>446253</v>
       </c>
       <c r="R56" t="n">
-        <v>6585635</v>
+        <v>6585661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7191,12 +7197,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ihopsjunken fruktkropp. Torrt i marken och snöfritt sen länge.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7205,7 +7206,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7226,6 +7226,115 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128931100</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92812</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>446300</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6585662</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92843</v>
+        <v>92845</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92845</v>
+        <v>92849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7231,7 +7231,7 @@
         <v>128931100</v>
       </c>
       <c r="B57" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84085</v>
+        <v>84091</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84085</v>
+        <v>84091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7571,6 +7571,125 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131760035</v>
+      </c>
+      <c r="B60" t="n">
+        <v>84092</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>446322</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6585654</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84091</v>
+        <v>84092</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84091</v>
+        <v>84092</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84092</v>
+        <v>84095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84092</v>
+        <v>84095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>131760035</v>
       </c>
       <c r="B60" t="n">
-        <v>84092</v>
+        <v>84095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84095</v>
+        <v>84097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84095</v>
+        <v>84097</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>131760035</v>
       </c>
       <c r="B60" t="n">
-        <v>84095</v>
+        <v>84097</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84097</v>
+        <v>84100</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84097</v>
+        <v>84100</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>131760035</v>
       </c>
       <c r="B60" t="n">
-        <v>84097</v>
+        <v>84100</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84100</v>
+        <v>84105</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84100</v>
+        <v>84105</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>131760035</v>
       </c>
       <c r="B60" t="n">
-        <v>84100</v>
+        <v>84105</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7340,7 +7340,7 @@
         <v>131487190</v>
       </c>
       <c r="B58" t="n">
-        <v>84105</v>
+        <v>84107</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>131487197</v>
       </c>
       <c r="B59" t="n">
-        <v>84105</v>
+        <v>84107</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>131760035</v>
       </c>
       <c r="B60" t="n">
-        <v>84105</v>
+        <v>84107</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7690,6 +7690,567 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132234186</v>
+      </c>
+      <c r="B61" t="n">
+        <v>84107</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>446075</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6585729</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>25 st inom 6 m omkrets.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132234168</v>
+      </c>
+      <c r="B62" t="n">
+        <v>84107</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>446256</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6585703</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>11 st inom 4 m omkrets.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132234147</v>
+      </c>
+      <c r="B63" t="n">
+        <v>84107</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>446221</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6585699</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>25 st i en omkrets av 6m.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132234208</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91272</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>446092</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6585678</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132234199</v>
+      </c>
+      <c r="B65" t="n">
+        <v>84107</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>446095</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6585628</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7576,7 +7576,7 @@
         <v>131760035</v>
       </c>
       <c r="B60" t="n">
-        <v>84146</v>
+        <v>84148</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>132234186</v>
       </c>
       <c r="B61" t="n">
-        <v>84146</v>
+        <v>84148</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>132234168</v>
       </c>
       <c r="B62" t="n">
-        <v>84146</v>
+        <v>84148</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>132234147</v>
       </c>
       <c r="B63" t="n">
-        <v>84146</v>
+        <v>84148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>132234199</v>
       </c>
       <c r="B65" t="n">
-        <v>84146</v>
+        <v>84148</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7695,7 +7695,7 @@
         <v>132234186</v>
       </c>
       <c r="B61" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>132234168</v>
       </c>
       <c r="B62" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>132234147</v>
       </c>
       <c r="B63" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91316</v>
+        <v>91322</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>132234199</v>
       </c>
       <c r="B65" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7695,7 +7695,7 @@
         <v>132234186</v>
       </c>
       <c r="B61" t="n">
-        <v>84150</v>
+        <v>84158</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>132234168</v>
       </c>
       <c r="B62" t="n">
-        <v>84150</v>
+        <v>84158</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>132234147</v>
       </c>
       <c r="B63" t="n">
-        <v>84150</v>
+        <v>84158</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91322</v>
+        <v>91332</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>132234199</v>
       </c>
       <c r="B65" t="n">
-        <v>84150</v>
+        <v>84158</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91332</v>
+        <v>91333</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7695,7 +7695,7 @@
         <v>132234186</v>
       </c>
       <c r="B61" t="n">
-        <v>84158</v>
+        <v>84159</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>132234168</v>
       </c>
       <c r="B62" t="n">
-        <v>84158</v>
+        <v>84159</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>132234147</v>
       </c>
       <c r="B63" t="n">
-        <v>84158</v>
+        <v>84159</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91333</v>
+        <v>91334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>132234199</v>
       </c>
       <c r="B65" t="n">
-        <v>84158</v>
+        <v>84159</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7695,7 +7695,7 @@
         <v>132234186</v>
       </c>
       <c r="B61" t="n">
-        <v>84159</v>
+        <v>84161</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>132234168</v>
       </c>
       <c r="B62" t="n">
-        <v>84159</v>
+        <v>84161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>132234147</v>
       </c>
       <c r="B63" t="n">
-        <v>84159</v>
+        <v>84161</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91334</v>
+        <v>91336</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>132234199</v>
       </c>
       <c r="B65" t="n">
-        <v>84159</v>
+        <v>84161</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -7695,7 +7695,7 @@
         <v>132234186</v>
       </c>
       <c r="B61" t="n">
-        <v>84161</v>
+        <v>84162</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>132234168</v>
       </c>
       <c r="B62" t="n">
-        <v>84161</v>
+        <v>84162</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>132234147</v>
       </c>
       <c r="B63" t="n">
-        <v>84161</v>
+        <v>84162</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>132234208</v>
       </c>
       <c r="B64" t="n">
-        <v>91336</v>
+        <v>91337</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>132234199</v>
       </c>
       <c r="B65" t="n">
-        <v>84161</v>
+        <v>84162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2023 artfynd.xlsx
+++ b/artfynd/A 53130-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115823879</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122878312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401890</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401891</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401892</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401893</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401894</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401905</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1796,6 +1846,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406370</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406600</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406601</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2149,6 +2214,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406603</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2265,6 +2335,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406604</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2373,6 +2448,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7230886</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2481,6 +2561,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7230892</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2589,6 +2674,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7230894</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2699,6 +2789,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240452</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2809,6 +2904,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240462</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2919,6 +3019,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240469</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240473</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3139,6 +3249,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240487</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3249,6 +3364,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240495</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3359,6 +3479,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240499</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3469,6 +3594,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240513</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3570,6 +3700,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478265</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3679,6 +3814,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76756387</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3788,6 +3928,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76794772</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3899,6 +4044,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84276184</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4011,6 +4161,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108051101</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4130,6 +4285,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108051192</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4246,6 +4406,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108051312</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4362,6 +4527,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108052857</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4481,6 +4651,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108052953</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4597,6 +4772,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108052996</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4713,6 +4893,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108053203</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4829,6 +5014,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108054296</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4938,6 +5128,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110632097</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5047,6 +5242,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115054916</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5161,6 +5361,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115823845</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5270,6 +5475,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115824272</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5398,6 +5608,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115877640</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5526,6 +5741,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115877666</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5659,6 +5879,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115877895</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5775,6 +6000,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971928</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5896,6 +6126,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971953</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6012,6 +6247,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971967</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6128,6 +6368,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971973</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6244,6 +6489,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115972386</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6360,6 +6610,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115972598</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6476,6 +6731,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115972621</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6582,6 +6842,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046257</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6688,6 +6953,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046261</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6794,6 +7064,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046270</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6900,6 +7175,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046272</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7006,6 +7286,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122881169</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7112,6 +7397,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122881299</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7221,6 +7511,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122901044</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7330,6 +7625,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122901055</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7445,6 +7745,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379164</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7558,6 +7863,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516486</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7664,6 +7974,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123519052</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7792,6 +8107,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123935663</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7912,6 +8232,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123935938</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8032,6 +8357,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123936010</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8152,6 +8482,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123936133</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8270,6 +8605,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131487189</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8388,6 +8728,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131487190</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8506,6 +8851,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131487193</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8624,6 +8974,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131487197</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8743,6 +9098,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131760035</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8858,6 +9218,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234137</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8973,6 +9338,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234147</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9088,6 +9458,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234168</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9203,6 +9578,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234186</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9313,6 +9693,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234199</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9419,6 +9804,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132285613</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9532,6 +9922,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70565260</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9641,6 +10036,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291509</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9750,6 +10150,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115823800</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9856,6 +10261,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132234208</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9965,6 +10375,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291497</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10065,6 +10480,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65421343</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10178,6 +10598,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111459073</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10287,6 +10712,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128931100</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10394,6 +10824,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115973638</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10501,6 +10936,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115974494</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10620,6 +11060,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379163</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10739,6 +11184,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123379162</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10837,6 +11287,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108431290</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10939,6 +11394,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291488</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11049,6 +11509,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115823909</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11159,6 +11624,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115823945</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11280,6 +11750,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971784</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11396,6 +11871,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971786</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11512,6 +11992,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971826</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11628,6 +12113,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971829</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11744,6 +12234,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115971880</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11850,6 +12345,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115972015</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11962,8 +12462,115 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123936321</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>